--- a/artfynd/A 12294-2025 artfynd.xlsx
+++ b/artfynd/A 12294-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99006574</v>
+        <v>99006699</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,11 +703,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -723,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>381045.1407595046</v>
+        <v>381045</v>
       </c>
       <c r="R2" t="n">
-        <v>6698613.860858328</v>
+        <v>6698614</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -756,24 +747,14 @@
           <t>1985-06-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1985-06-24</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>10-20 ex</t>
+          <t>Källflöde</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,40 +782,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99006586</v>
+        <v>99006657</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>381045.1407595046</v>
+        <v>381045</v>
       </c>
       <c r="R3" t="n">
-        <v>6698613.860858328</v>
+        <v>6698614</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,19 +858,9 @@
           <t>1985-06-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1985-06-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,15 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99007697</v>
+        <v>99006684</v>
       </c>
       <c r="B4" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,16 +899,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222395</v>
+        <v>222002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>381045.1407595046</v>
+        <v>381045</v>
       </c>
       <c r="R4" t="n">
-        <v>6698613.860858328</v>
+        <v>6698614</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -992,22 +957,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1985-07-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-06-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1985-07-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-06-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,15 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99006684</v>
+        <v>99007697</v>
       </c>
       <c r="B5" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1006,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222002</v>
+        <v>222395</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>381045.1407595046</v>
+        <v>381045</v>
       </c>
       <c r="R5" t="n">
-        <v>6698613.860858328</v>
+        <v>6698614</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1109,27 +1064,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1985-06-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-07-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1985-06-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>"Mycket"</t>
+          <t>1985-07-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,15 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99006657</v>
+        <v>99006574</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,26 +1108,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1205,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>381045.1407595046</v>
+        <v>381045</v>
       </c>
       <c r="R6" t="n">
-        <v>6698613.860858328</v>
+        <v>6698614</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1238,19 +1173,14 @@
           <t>1985-06-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1985-06-24</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>10-20 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,15 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99006645</v>
+        <v>99006586</v>
       </c>
       <c r="B7" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1322,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>381045.1407595046</v>
+        <v>381045</v>
       </c>
       <c r="R7" t="n">
-        <v>6698613.860858328</v>
+        <v>6698614</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1355,24 +1280,9 @@
           <t>1985-06-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1985-06-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Stora, kraftiga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,6 +1307,113 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>99006645</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hult, SV Mangen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>381045</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6698614</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1985-06-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1985-06-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stora, kraftiga</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12294-2025 artfynd.xlsx
+++ b/artfynd/A 12294-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99006699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99006657</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99006684</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99007697</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99006574</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99006586</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,8 +1449,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99006645</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>